--- a/outputs/cf01_annotation_20260728/track_a_human_blind_annotation.xlsx
+++ b/outputs/cf01_annotation_20260728/track_a_human_blind_annotation.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R9f8f28bbdaa847ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工盲标" sheetId="2" r:id="R549b95e60430495a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签字典" sheetId="3" r:id="Rfcf977bd8e2248df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R0311a5d9c21f4400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工盲标" sheetId="2" r:id="R2a5f43b20c6e45ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="标签字典" sheetId="3" r:id="R499f0fad41724aaf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -330,7 +330,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Codex" id="{80C1D5FB-59CF-418F-83D0-0C7B3BDB9166}"/>
+  <xltc:person displayName="Codex" id="{4E573F07-8A6B-4E9E-8EA0-656BE4BCDEF6}"/>
 </xltc:personList>
 </file>
 
@@ -1431,7 +1431,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra756935b13bc49f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e034f38e620470e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
